--- a/docs/legal-acts/export/EU 2025-1929.xlsx
+++ b/docs/legal-acts/export/EU 2025-1929.xlsx
@@ -473,7 +473,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21 18:24</t>
+          <t>2026-10-21 18:31</t>
         </is>
       </c>
     </row>
@@ -2553,7 +2553,7 @@
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
@@ -2739,7 +2739,7 @@
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
@@ -2832,7 +2832,7 @@
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
@@ -2925,7 +2925,7 @@
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
@@ -3018,7 +3018,7 @@
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr">
@@ -3204,7 +3204,7 @@
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G29" s="3" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
@@ -3390,7 +3390,7 @@
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr">
@@ -3483,7 +3483,7 @@
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G33" s="3" t="inlineStr">
@@ -3669,7 +3669,7 @@
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr">
@@ -3762,7 +3762,7 @@
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
@@ -3855,7 +3855,7 @@
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
@@ -3948,7 +3948,7 @@
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G37" s="3" t="inlineStr">
@@ -4041,7 +4041,7 @@
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
@@ -4134,7 +4134,7 @@
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G39" s="3" t="inlineStr">
@@ -4227,7 +4227,7 @@
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
@@ -4320,7 +4320,7 @@
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G41" s="3" t="inlineStr">
@@ -4413,7 +4413,7 @@
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
@@ -4506,7 +4506,7 @@
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G43" s="3" t="inlineStr">
@@ -4599,7 +4599,7 @@
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G44" s="3" t="inlineStr">
@@ -4692,7 +4692,7 @@
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G45" s="3" t="inlineStr">
@@ -4785,7 +4785,7 @@
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
@@ -4878,7 +4878,7 @@
       </c>
       <c r="F47" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G47" s="3" t="inlineStr">
@@ -4971,7 +4971,7 @@
       </c>
       <c r="F48" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G48" s="3" t="inlineStr">
@@ -5064,7 +5064,7 @@
       </c>
       <c r="F49" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G49" s="3" t="inlineStr">
@@ -5157,7 +5157,7 @@
       </c>
       <c r="F50" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G50" s="3" t="inlineStr">
@@ -5250,7 +5250,7 @@
       </c>
       <c r="F51" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G51" s="3" t="inlineStr">
@@ -5343,7 +5343,7 @@
       </c>
       <c r="F52" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G52" s="3" t="inlineStr">
@@ -5436,7 +5436,7 @@
       </c>
       <c r="F53" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G53" s="3" t="inlineStr">
@@ -5529,7 +5529,7 @@
       </c>
       <c r="F54" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G54" s="3" t="inlineStr">
@@ -5622,7 +5622,7 @@
       </c>
       <c r="F55" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G55" s="3" t="inlineStr">
@@ -5715,7 +5715,7 @@
       </c>
       <c r="F56" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G56" s="3" t="inlineStr">
@@ -5808,7 +5808,7 @@
       </c>
       <c r="F57" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G57" s="3" t="inlineStr">
@@ -5901,7 +5901,7 @@
       </c>
       <c r="F58" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G58" s="3" t="inlineStr">
@@ -5994,7 +5994,7 @@
       </c>
       <c r="F59" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G59" s="3" t="inlineStr">
@@ -6087,7 +6087,7 @@
       </c>
       <c r="F60" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G60" s="3" t="inlineStr">
@@ -6180,7 +6180,7 @@
       </c>
       <c r="F61" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G61" s="3" t="inlineStr">
@@ -6273,7 +6273,7 @@
       </c>
       <c r="F62" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G62" s="3" t="inlineStr">
@@ -6366,7 +6366,7 @@
       </c>
       <c r="F63" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G63" s="3" t="inlineStr">
@@ -6459,7 +6459,7 @@
       </c>
       <c r="F64" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G64" s="3" t="inlineStr">
@@ -6552,7 +6552,7 @@
       </c>
       <c r="F65" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G65" s="3" t="inlineStr">
@@ -6645,7 +6645,7 @@
       </c>
       <c r="F66" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G66" s="3" t="inlineStr">
@@ -6738,7 +6738,7 @@
       </c>
       <c r="F67" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G67" s="3" t="inlineStr">
@@ -6831,7 +6831,7 @@
       </c>
       <c r="F68" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G68" s="3" t="inlineStr">
@@ -6924,7 +6924,7 @@
       </c>
       <c r="F69" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G69" s="3" t="inlineStr">
@@ -7017,7 +7017,7 @@
       </c>
       <c r="F70" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G70" s="3" t="inlineStr">
@@ -7110,7 +7110,7 @@
       </c>
       <c r="F71" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G71" s="3" t="inlineStr">
@@ -7203,7 +7203,7 @@
       </c>
       <c r="F72" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G72" s="3" t="inlineStr">
@@ -7296,7 +7296,7 @@
       </c>
       <c r="F73" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G73" s="3" t="inlineStr">
@@ -7389,7 +7389,7 @@
       </c>
       <c r="F74" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G74" s="3" t="inlineStr">
@@ -7482,7 +7482,7 @@
       </c>
       <c r="F75" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G75" s="3" t="inlineStr">
@@ -7575,7 +7575,7 @@
       </c>
       <c r="F76" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G76" s="3" t="inlineStr">
@@ -7668,7 +7668,7 @@
       </c>
       <c r="F77" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G77" s="3" t="inlineStr">
@@ -7761,7 +7761,7 @@
       </c>
       <c r="F78" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G78" s="3" t="inlineStr">
@@ -7854,7 +7854,7 @@
       </c>
       <c r="F79" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G79" s="3" t="inlineStr">
@@ -7947,7 +7947,7 @@
       </c>
       <c r="F80" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G80" s="3" t="inlineStr">
@@ -8040,7 +8040,7 @@
       </c>
       <c r="F81" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G81" s="3" t="inlineStr">
@@ -8133,7 +8133,7 @@
       </c>
       <c r="F82" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G82" s="3" t="inlineStr">
